--- a/big firm analysis/big_firm_analysis_results.xlsx
+++ b/big firm analysis/big_firm_analysis_results.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,11 +525,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>customer_support</t>
+          <t>customer_support_experience</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -548,17 +548,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>chatbot,NLP,automation,machine learning</t>
+          <t>chatbot,NLP,machine learning,automation</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Improved customer service efficiency and enhanced customer satisfaction through AI-powered support tools.</t>
+          <t>BT expects faster response times, higher customer satisfaction, and reduced support costs by automating routine inquiries and providing real‑time assistance.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>BT Group is leveraging AI technology from Sprinklr to transform its customer service experience. This initiative represents a strategic investment in AI-driven customer support capabilities aimed at improving service quality and operational efficiency for the UK telecommunications provider.</t>
+          <t>BT is deploying AI‑powered customer service solutions in partnership with Sprinklr to transform its support experience. The system uses natural language processing and machine learning to power chatbots and automated assistance, enabling quicker, more accurate responses to customer queries. This initiative is a high‑impact move to improve customer satisfaction and operational efficiency.</t>
         </is>
       </c>
     </row>
@@ -584,11 +584,11 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,17 +607,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>automation,machine learning,RPA,data processing</t>
+          <t>machine learning,automation</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Improved operational efficiency and cost reduction through AI automation of manual data processing tasks to reverse business unit declines.</t>
+          <t>Accelerates data processing, reduces manual effort, and helps reverse business unit decline by improving operational efficiency.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>BT is expanding AI adoption to automate manual data processing within a struggling business unit. This strategic initiative aims to reverse performance declines by enhancing operational efficiency. The move represents a focused application of AI for internal business transformation and turnaround.</t>
+          <t>BT is deploying AI to automate manual data processing tasks within a business unit to reverse performance declines. The AI leverages machine learning and automation to streamline data workflows, reducing errors and speeding up decision-making. This initiative aims to boost productivity and restore growth.</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>cybersecurity</t>
+          <t>security_fraud_threat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -666,17 +666,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>machine learning,anomaly detection,automation,threat detection</t>
+          <t>machine learning,anomaly detection,threat detection,intrusion detection</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Enhanced security for business customers, reducing risk of data breaches and strengthening BT's competitive position in the enterprise market.</t>
+          <t>By deploying AI-driven threat detection, BT aims to reduce hacking incidents for business customers, safeguarding their data and revenue.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>BT is scaling up its AI-powered cybersecurity capabilities to protect business customers from hacking threats. This initiative represents a strategic investment in AI-driven threat detection and response. The move strengthens BT's value proposition for enterprise clients by enhancing their security posture.</t>
+          <t>BT is expanding its use of AI to counter hacking threats faced by its business customers. The company employs machine learning and anomaly detection to identify and mitigate cyber attacks in real time. This initiative strengthens customer trust and protects critical business data, positioning BT as a secure partner in the telecom market.</t>
         </is>
       </c>
     </row>
@@ -702,11 +702,11 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>network_optimization</t>
+          <t>network_optimization_performance</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -725,17 +725,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>machine learning,predictive analytics,automation,neural networks</t>
+          <t>machine learning,automation,predictive analytics</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Enhanced network efficiency, reliability, and performance through AI-driven automation and optimization.</t>
+          <t>Enhanced network performance and reliability through AI-driven optimization, leading to improved service quality and reduced operational costs.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>BT is embedding AI at the core of its network platform strategy, representing a fundamental shift in network operations. This initiative demonstrates BT's commitment to leveraging artificial intelligence for comprehensive network transformation and optimization.</t>
+          <t>BT is embedding AI into its network platform to drive operational excellence. The AI-powered platform applies machine learning and automation to optimize network performance in real‑time, enabling self‑optimizing capabilities and predictive insights. This initiative is expected to boost service quality, reduce outages, and lower operational costs.</t>
         </is>
       </c>
     </row>
@@ -761,11 +761,11 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>customer_support</t>
+          <t>customer_support_experience</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -779,22 +779,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>scaled</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>chatbot,NLP,machine learning,automation</t>
+          <t>chatbot,NLP,automation,LLM</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Reduced operational costs and improved customer satisfaction through automated support and faster query resolution.</t>
+          <t>BT is enhancing customer service efficiency and satisfaction by deploying AI-powered chatbots and virtual assistants, reducing response times and operational costs.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>BT Group has made AI-powered customer service a cornerstone of its corporate digital transformation strategy. This initiative deploys intelligent support tools to enhance customer experience and operational efficiency. The progress report demonstrates BT's commitment to leveraging AI and Agile methodologies at scale.</t>
+          <t>BT Group is integrating AI-driven chatbots and virtual assistants into its customer service operations as part of a broader digital transformation. These tools use natural language processing and automation to handle routine queries and support tickets, improving response times and freeing staff for more complex issues. This initiative is a key component of BT’s strategy to deliver faster, more personalized customer experiences.</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -843,17 +843,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>generative AI,code generation,automation</t>
+          <t>generative AI,LLM,code generation,Amazon CodeWhisperer</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Accelerated software development cycles and enhanced developer productivity across BT's engineering teams.</t>
+          <t>Enables BT developers to write code faster and with fewer errors, accelerating project delivery and reducing development costs.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>BT is expanding its deployment of Amazon's generative AI developer tool to a wider group of coders within the organization. This initiative focuses on improving internal developer productivity and streamlining software development workflows. The rollout represents a strategic investment in AI-powered tooling to boost operational efficiency in BT's technology operations.</t>
+          <t>BT is deploying Amazon’s generative AI developer tool, likely CodeWhisperer, to a broader group of internal coders. The AI assists developers by auto‑suggesting code snippets and reducing manual effort, boosting productivity across engineering teams. This initiative improves development speed and quality, supporting BT’s broader digital transformation goals.</t>
         </is>
       </c>
     </row>
@@ -879,20 +879,20 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>machine learning,automation,NLP,analytics</t>
+          <t>generative AI,LLM,automation</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Building internal AI capabilities to drive future operational efficiency and innovation.</t>
+          <t>By training employees in AI, BT aims to boost workforce efficiency and enable staff to adopt AI tools for faster decision‑making and process automation.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>BT executives are discussing AI training programs for employees to build internal capabilities. This initiative focuses on upskilling the workforce to leverage AI technologies for operational improvements. It represents a strategic investment in human capital to support digital transformation.</t>
+          <t>BT is rolling out an AI training program for its employees, focusing on generative AI and large language models. The initiative equips staff with the skills to integrate AI into their daily workflows, improving productivity and fostering a culture of innovation.</t>
         </is>
       </c>
     </row>
@@ -938,15 +938,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -961,17 +961,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>GenAI,AI platform,model orchestration,API integration</t>
+          <t>generative AI,LLM,model-agnostic platform,automation</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ensures strategic flexibility and cost control by avoiding vendor lock-in for AI capabilities.</t>
+          <t>Enables BT to flexibly deploy generative AI models across business functions without vendor lock‑in, improving innovation speed and cost efficiency.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>BT has implemented a platform-based approach to generative AI that enables them to switch between different underlying models, avoiding vendor lock-in. This strategy provides flexibility to choose the best models for specific tasks and maintains negotiating power with AI providers. The initiative represents a foundational investment in AI infrastructure that will support multiple future use cases across the organization.</t>
+          <t>BT has built a generative AI platform that permits the use of any underlying model, thereby avoiding vendor lock‑in. The platform powers internal AI applications, giving staff the flexibility to choose the best model for each task. This strategy supports BT’s goal of maintaining agility and cost‑effectiveness in its AI initiatives.</t>
         </is>
       </c>
     </row>
@@ -997,11 +997,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1020,17 +1020,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>generative AI,machine learning,automation</t>
+          <t>automation,machine learning,generative AI</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Reduces AI project deployment time to 14 days, enabling rapid innovation and faster realization of AI value across the organization.</t>
+          <t>Accelerating AI project delivery by 14 days reduces time‑to‑market, boosts innovation speed, and cuts development costs across BT’s digital initiatives.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>BT Group's Digital unit has established an AI Accelerator capability that dramatically speeds up AI project launches to within 14 days. The initiative focuses on accelerating various AI use cases including generative AI applications. This represents a strategic investment in operational agility and enterprise-wide AI enablement.</t>
+          <t>BT Digital has launched an AI Accelerator that enables teams to launch AI projects within 14 days, streamlining internal workflows. By automating the early stages of AI development and leveraging machine learning and generative AI, the initiative speeds up deployment of new AI solutions, enhancing BT’s competitive edge.</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>cybersecurity</t>
+          <t>security_fraud_threat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1079,17 +1079,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>machine learning,voice biometrics,pattern recognition,NLP</t>
+          <t>voice biometrics,machine learning,AI</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Reduced financial losses from voice fraud and enhanced security for BT's voice communication services.</t>
+          <t>By leveraging AI-powered voice biometrics, BT aims to significantly reduce voice fraud incidents, safeguarding revenue and enhancing customer trust.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>BT has partnered with Pindrop to deploy AI-powered voice fraud detection technology. This cybersecurity initiative aims to protect BT's telecommunications infrastructure from voice-based threats. The partnership represents a strategic investment in AI-driven security measures to combat evolving fraud techniques.</t>
+          <t>BT has partnered with Pindrop to deploy AI-driven voice biometrics for fraud detection in voice communications. The solution analyzes call patterns and speaker characteristics to identify and block fraudulent activity in real time, protecting both customers and the company’s revenue streams.</t>
         </is>
       </c>
     </row>
@@ -1115,11 +1115,11 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1138,17 +1138,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>machine learning,NLP,automation,personalization</t>
+          <t>machine learning,NLP,adaptive learning,automation</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Enhanced employee skills and productivity through personalized, AI-driven training programs.</t>
+          <t>The AI‑enhanced training platform accelerates employee onboarding and skill development, reducing training time and improving workforce competency.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>BT is implementing an AI-enhanced training platform to improve internal productivity and workforce development. This initiative reflects BT's strategic focus on upskilling employees through advanced AI technologies, enabling more efficient and personalized learning experiences.</t>
+          <t>BT has rolled out an AI‑enhanced training platform to support its communications business. The solution leverages machine learning and natural language processing to deliver adaptive, personalized learning experiences for staff. This initiative boosts internal productivity by speeding up training and upskilling across the organization.</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>automation,machine learning,NLP,workflow automation</t>
+          <t>NLP,machine learning,automation,virtual assistant</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Enhanced staff productivity and operational efficiency through AI-powered automation of internal processes.</t>
+          <t>Enhances staff efficiency by automating routine tasks and providing AI‑driven support, reducing manual effort and speeding up internal processes.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>BT Group is deploying ServiceNow's AI platform to enhance staff operations and improve internal productivity. This initiative focuses on automating internal workflows and processes to drive operational efficiency. The move represents a significant investment in employee-facing AI technology to streamline BT's internal operations.</t>
+          <t>BT Group is deploying ServiceNow AI to streamline staff operations, leveraging natural language processing and machine learning to automate workflows and offer virtual assistance. This initiative improves internal productivity and reduces the time employees spend on repetitive tasks.</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>network_optimization</t>
+          <t>network_optimization_performance</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1249,22 +1249,22 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>machine learning,automation,predictive analytics</t>
+          <t>machine learning,automation,network analytics,predictive analytics</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Enhanced network efficiency and customer experience through AI-driven operations.</t>
+          <t>Enhanced network performance and reliability, resulting in improved customer experience and greater operational efficiency for BT.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>BT has partnered with Nokia to implement AI-powered network optimization solutions that aim to deliver superior customer experience and improve operational efficiency. This strategic initiative focuses on transforming core network operations through artificial intelligence. The partnership represents a significant investment in AI for critical telecom infrastructure.</t>
+          <t>BT has teamed up with Nokia to deploy AI‑driven network optimization solutions that automatically adjust traffic, balance loads, and reduce latency. By applying machine learning and predictive analytics to network operations, the partnership aims to deliver a superior customer experience while streamlining operational processes.</t>
         </is>
       </c>
     </row>
@@ -1294,11 +1294,11 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>automation,machine learning,predictive analytics,data analytics</t>
+          <t>machine learning,automation,predictive analytics</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Streamlined procurement processes, reduced costs, and improved supplier management through AI-driven automation and analytics.</t>
+          <t>Streamlined BT’s procurement processes, reducing cycle times and costs while enhancing supplier insight and decision‑making.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>BT Sourced, a BT subsidiary, is leading a procurement transformation initiative powered by AI, automation, and analytics. This strategic move aims to modernize purchasing and supply chain operations across the telecommunications company. The initiative represents a significant investment in operational efficiency and cost optimization.</t>
+          <t>BT Sourced is leveraging AI, automation and analytics to transform its procurement function. The solution applies machine learning to analyze spend data, automate supplier selection and contract workflows, and predict optimal sourcing decisions. This initiative drives significant cost savings and operational efficiency across BT’s supply chain.</t>
         </is>
       </c>
     </row>
@@ -1353,11 +1353,11 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1366,27 +1366,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>pilot</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>automation,machine learning,NLP</t>
+          <t>machine learning,predictive analytics,automation</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Enhanced procurement efficiency and cost savings through AI-driven supplier management and sourcing optimization.</t>
+          <t>Streamlined procurement processes, reducing cycle times and costs through AI-driven supplier insights.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>BT has partnered with Globality to implement AI-powered procurement solutions, aiming to transform their sourcing and supplier management processes. This initiative represents a strategic move to leverage AI for operational excellence and significant cost reduction in BT's procurement function.</t>
+          <t>BT has partnered with Globality to deploy AI‑driven procurement solutions that leverage machine learning and predictive analytics. The initiative aims to automate supplier selection, forecast demand, and optimize spend, thereby improving efficiency and cost control across the organization.</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>customer_support</t>
+          <t>customer_support_experience</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>chatbot,NLP,automation,machine learning</t>
+          <t>chatbot,NLP,automation,AI virtual assistant</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Enhanced customer service efficiency and improved support for vulnerable customers through AI-powered tools.</t>
+          <t>Accelerates response times and improves satisfaction for all customers, especially the most vulnerable, by automating routine queries and providing personalized support.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Virgin Media O2 has launched new AI tools to enhance customer service operations, with specific focus on improving support for vulnerable customers. This deployment represents a significant investment in AI-powered customer service capabilities aimed at transforming the customer experience.</t>
+          <t>Virgin Media O2 is rolling out AI-powered chatbots and virtual assistants to enhance customer service. These tools use natural language processing and automation to handle common issues quickly and offer tailored help to vulnerable customers, positioning the company as a leader in customer‑centric AI adoption.</t>
         </is>
       </c>
     </row>
@@ -1471,11 +1471,11 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>network_optimization</t>
+          <t>network_optimization_performance</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1494,17 +1494,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>machine learning,predictive analytics,automation</t>
+          <t>machine learning,predictive analytics,network analytics,AI</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Enhanced broadband network performance and reliability leading to improved customer satisfaction and operational efficiency.</t>
+          <t>Enhances broadband reliability and quality by enabling real‑time network optimization, reducing latency and preventing service disruptions.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>VMO2 is deploying AI-powered network intelligence to strengthen broadband service delivery across its network. This initiative leverages machine learning to optimize network performance and reliability. The move signals a major strategic push toward AI-driven infrastructure management in the competitive UK telecommunications market.</t>
+          <t>Virgin Media O2 is deploying AI‑powered network intelligence to monitor and optimize broadband performance. The system uses machine learning and predictive analytics to detect anomalies, balance traffic, and improve QoS across its network. This initiative strengthens service delivery and positions the company to better meet customer expectations.</t>
         </is>
       </c>
     </row>
@@ -1530,11 +1530,11 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>analytics</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1543,27 +1543,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Generative AI,NLP,automation</t>
+          <t>generative AI,LLM,NLP,automation</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Automated risk reporting and enhanced risk analysis capabilities for improved decision-making and regulatory compliance.</t>
+          <t>Enhances the accuracy, speed, and consistency of risk reporting, enabling faster decision-making and stronger compliance.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>VMO2 is implementing Generative AI to transform its risk management and reporting processes. This strategic initiative aims to enhance internal data analysis capabilities and automate the generation of risk insights for better governance in the UK telecom market.</t>
+          <t>Virgin Media O2 is deploying generative AI to transform its risk management processes. The AI system automatically generates risk reports using natural language generation, reducing manual effort and improving accuracy. This initiative strengthens compliance, risk visibility, and decision speed across the organization.</t>
         </is>
       </c>
     </row>
@@ -1589,11 +1589,11 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1612,17 +1612,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AI,machine learning,automation</t>
+          <t>machine learning,AI training,automation</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Upskilling employees with AI capabilities to improve internal productivity and operational efficiency.</t>
+          <t>Equipping employees with AI skills improves internal productivity and enables more efficient use of AI tools across the organisation.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Virgin Media O2 is implementing an AI training program for employees as part of its enhanced learning and development initiative. This move aims to equip its workforce with critical AI skills necessary for modern telecommunications operations. The program represents a strategic investment in human capital to support digital transformation.</t>
+          <t>Virgin Media O2 has rolled out an AI training component within its learning and development programme to equip staff with critical AI skills. The initiative focuses on internal productivity, enabling employees to apply AI and automation in their day‑to‑day work, thereby boosting overall operational efficiency.</t>
         </is>
       </c>
     </row>
@@ -1648,11 +1648,11 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>network_optimization</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1671,17 +1671,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>machine learning,automation,predictive analytics,anomaly detection</t>
+          <t>machine learning,automation</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Enhanced network performance and reliability while reducing operational costs through AI-driven automation.</t>
+          <t>Accelerated network operations, reducing manual effort and improving response times.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>VMO2 is leveraging AI and automation to accelerate their network operations, representing a strategic push toward intelligent network management. This initiative focuses on optimizing network performance and operational efficiency through advanced analytics and automated processes. The move signals VMO2's commitment to modernizing their core infrastructure with emerging technologies.</t>
+          <t>VMO2 is deploying AI and automation to streamline its network operations, enabling faster task completion and reduced human intervention. By leveraging machine learning models and automated workflows, the company enhances operational efficiency and responsiveness.</t>
         </is>
       </c>
     </row>
@@ -1707,11 +1707,11 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>customer_support</t>
+          <t>customer_support_experience</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1730,17 +1730,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>machine learning,personalization,recommendation engine,automation</t>
+          <t>chatbot,NLP,automation</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Enhanced in-store customer experience leading to increased satisfaction and sales conversion.</t>
+          <t>Enhanced in‑store customer interactions, reducing wait times and boosting satisfaction and sales conversion rates.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>VMO2 is launching AI-powered technology in retail stores to transform customer experiences. This strategic initiative focuses on leveraging artificial intelligence to personalize interactions and optimize service delivery in physical retail environments.</t>
+          <t>Virgin Media O2 has introduced an AI‑powered solution for its O2 Business stores, leveraging chatbots and natural language processing to provide instant, personalised assistance to shoppers. By automating routine queries and guiding customers through product choices, the technology elevates the in‑store experience and drives higher engagement and sales.</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>customer_support_experience</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1789,17 +1789,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>NLP,generative AI,conversational search,AI assistant</t>
+          <t>LLM,NLP,AI search</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Creates new revenue stream through AI-powered search add-on service for customers.</t>
+          <t>Enables Virgin Media O2 to offer customers an AI-powered search tool as a new add‑on, boosting engagement and creating an additional revenue stream.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>VMO2 has partnered with Perplexity to offer AI search access as an add-on service to customers. This represents a commercial AI product offering rather than internal operational use. The partnership allows VMO2 to leverage Perplexity's AI search technology to enhance their service portfolio.</t>
+          <t>Virgin Media O2 has partnered with Perplexity to provide AI search access to its customers. The service leverages large language models and natural language processing to deliver instant, contextual search results, enhancing the customer experience and opening a new product line.</t>
         </is>
       </c>
     </row>
@@ -1825,11 +1825,11 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>security_fraud_threat</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1848,17 +1848,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>chatbot,NLP,voice technology,automation,machine learning</t>
+          <t>chatbot,NLP,automation,AI</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Reduces fraud losses and protects vulnerable customers by automatically engaging and wasting scammers' time.</t>
+          <t>Reduces scam incidents and protects customers from fraud by proactively engaging and identifying scam attempts.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>VMO2's O2 brand has deployed an AI system, nicknamed 'AI granny', to combat phone scammers by engaging with them to waste their time. This innovative approach protects customers, particularly vulnerable populations, from fraud. The initiative represents a significant application of conversational AI for security purposes in the UK telecom sector.</t>
+          <t>O2 has deployed an AI-powered chatbot that impersonates an elderly woman—an "AI granny"—to lure and detect phone scammers. The system uses natural language processing to converse with potential fraudsters, flagging suspicious activity and preventing scams. This initiative enhances customer security and demonstrates O2’s commitment to innovative fraud prevention.</t>
         </is>
       </c>
     </row>
@@ -1884,11 +1884,11 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>security_fraud_threat</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1907,17 +1907,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>machine learning,NLP,automation</t>
+          <t>machine learning,natural language processing,automation</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Enhanced customer protection from spam and fraudulent communications, improving trust and network security.</t>
+          <t>The AI-powered spam detection tools reduce unwanted calls and messages, protecting customers and safeguarding revenue while improving overall user experience.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>VMO2 is deploying AI-powered spam fighting tools from Hiya to protect customers from unwanted and potentially fraudulent communications. This initiative represents an active rollout of security-focused AI technology to improve customer experience and network integrity.</t>
+          <t>VMO2 is deploying AI-driven spam fighting tools in partnership with Hiya to identify and block spam calls and messages. By leveraging machine learning and natural language processing, the system automatically classifies and filters suspicious traffic. This initiative enhances customer protection and preserves network integrity, delivering tangible benefits for both users and the company.</t>
         </is>
       </c>
     </row>
@@ -1943,11 +1943,11 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>other</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.95</v>
+        <v>0.65</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>VMO2 expects to save over £1 million annually through AI-optimized data centre cooling operations.</t>
+          <t>Virgin Media O2 expects to save over £1 million per year in data centre cooling costs through AI‑driven optimisation.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>VMO2 has partnered with EkkoSense to implement AI-driven optimization of their data centre cooling systems. This initiative is projected to generate over £1 million in annual energy savings. The project demonstrates VMO2's focus on using AI for operational efficiency and sustainability in their critical infrastructure.</t>
+          <t>Virgin Media O2 has partnered with EkkoSense to deploy AI‑powered analytics that optimise data‑centre cooling systems. By predicting temperature and load patterns, the solution reduces energy consumption, delivering significant cost savings and improving operational efficiency.</t>
         </is>
       </c>
     </row>
@@ -2002,11 +2002,11 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2025,17 +2025,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>MLOps,Vertex AI Pipelines,machine learning,automation,pipeline optimization</t>
+          <t>MLOps,Vertex AI Pipelines,machine learning,automation,cloud</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Accelerated AI model development and deployment cycles while improving operational efficiency and scalability.</t>
+          <t>Streamlined ML model deployment and reduced operational overhead, enabling faster AI project delivery across the organization.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>VMO2 has implemented MLOps practices using Vertex AI Pipelines to optimize and scale their machine learning environments. This initiative focuses on improving the efficiency and reliability of their AI model deployment processes. It represents a significant step in operationalizing AI at scale within the organization.</t>
+          <t>Virgin Media O2 has optimized its Vertex AI Pipelines environments to support large‑scale MLOps, improving the efficiency of model training, testing, and deployment. By automating pipeline workflows and scaling infrastructure, the team can deliver AI solutions more quickly and with lower maintenance costs, boosting internal productivity.</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>network_optimization</t>
+          <t>predictive_maintenance_analytics</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>machine learning,automation,predictive analytics,AIOps</t>
+          <t>machine learning,predictive analytics,automation,anomaly detection,network telemetry,AI Ops</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Enhanced network efficiency, reliability, and performance through intelligent automation and predictive capabilities.</t>
+          <t>Enables faster fault detection and automated remediation, reducing network downtime and improving service reliability.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>VMO2 is developing an AI strategy to power the network of the future, focusing on intelligent operations and automation. This initiative represents a significant investment in AI-driven network optimization and management capabilities. The strategy aims to transform how VMO2 operates and maintains its telecommunications infrastructure.</t>
+          <t>Virgin Media O2 is deploying an AI Ops framework that leverages machine learning and predictive analytics to monitor network health in real time. The system automatically detects anomalies, predicts equipment failures, and triggers self‑healing actions, thereby enhancing overall network performance and reliability.</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>customer_support</t>
+          <t>customer_support_experience</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2143,17 +2143,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>chatbot,NLP,virtual assistant,automation,conversational AI</t>
+          <t>chatbot,NLP,virtual assistant,automation,LLM</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Enhanced customer service efficiency and satisfaction through AI-powered automation and support.</t>
+          <t>By automating routine inquiries and providing instant, context‑aware responses, Vodafone is expected to reduce average handling time, increase first‑contact resolution rates, and boost overall customer satisfaction.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Vodafone is implementing AI-powered solutions to transform its customer service experience. This initiative represents a strategic push toward next-generation customer engagement through advanced automation and intelligent assistance. The project highlights Vodafone's focus on leveraging AI to improve customer satisfaction and operational efficiency.</t>
+          <t>Vodafone is deploying AI‑powered chatbots and virtual assistants that leverage natural language processing and large language models to handle customer queries in real time. This technology transforms the customer service experience by delivering faster, more accurate support and freeing human agents for complex issues, positioning Vodafone as a leader in next‑generation telecom customer care.</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>network_planning_deployment</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2202,17 +2202,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>generative AI,machine learning,automation,predictive analytics</t>
+          <t>generative AI,LLM,machine learning,automation</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Automating network lifecycle management improves operational efficiency, reduces manual effort, and enhances network reliability across Vodafone's infrastructure.</t>
+          <t>Generative AI accelerates network design and deployment, reducing planning time and improving coverage efficiency.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Vodafone is leveraging generative AI to enhance its network lifecycle management, representing a strategic partnership with Google Cloud. This initiative aims to transform how Vodafone plans, deploys, and maintains its network infrastructure through AI-driven automation and optimization.</t>
+          <t>Vodafone is leveraging generative AI and large language models to streamline its network lifecycle, from design to rollout. The AI assists in generating network plans, optimizing coverage, and accelerating deployment decisions, cutting planning time and enhancing network performance. This initiative positions Vodafone to deploy infrastructure more efficiently and maintain a competitive edge in the telecom market.</t>
         </is>
       </c>
     </row>
@@ -2238,20 +2238,20 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>machine learning,automation,AI training,digital skills</t>
+          <t>generative AI,LLM,NLP,automation,machine learning</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Improved workforce AI literacy enabling more efficient internal processes and accelerated AI adoption across operations.</t>
+          <t>Empowers Vodafone staff with AI capabilities, enhancing productivity, accelerating innovation, and improving internal processes across the organization.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Vodafone is implementing comprehensive AI training programs for employees as part of their digital modernization strategy. This initiative reflects a strategic investment in human capital to support AI-driven transformation and operational excellence.</t>
+          <t>Vodafone is rolling out AI training programs for its employees, leveraging generative AI and large language models to equip staff with advanced AI skills. The initiative focuses on internal productivity, enabling teams to automate routine tasks, generate insights, and develop AI-driven solutions. This investment positions the company to harness AI across its operations and maintain a competitive edge.</t>
         </is>
       </c>
     </row>
@@ -2297,15 +2297,15 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2315,22 +2315,22 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>pilot</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>automation,NLP,machine learning</t>
+          <t>automation,machine learning,NLP</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Streamlined recruitment process reducing time-to-hire and HR workload.</t>
+          <t>Accelerated recruitment by automating initial candidate screening, reducing time-to-hire and improving the quality of shortlisted applicants.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Vodafone has implemented automated systems to screen job candidates, applying AI technology to internal recruitment processes. This initiative focuses on using 'robots' to streamline hiring workflows and improve operational efficiency in HR. The adoption represents a shift toward automation of internal business functions in the telecommunications industry.</t>
+          <t>Vodafone deployed AI-powered robots to screen jobhunters, using machine learning and natural language processing to evaluate resumes and interview responses. The system automates the early stages of recruitment, freeing HR staff to focus on higher‑value tasks. This initiative enhances hiring efficiency and supports Vodafone’s talent acquisition strategy.</t>
         </is>
       </c>
     </row>
@@ -2356,11 +2356,11 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>network_optimization_performance</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2379,17 +2379,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>agentic AI,automation,machine learning</t>
+          <t>machine learning,automation,self-optimizing network</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Agentic AI will automate network operations, reducing manual workload and improving operational efficiency.</t>
+          <t>Automating network operations with agentic AI is expected to reduce downtime, lower operational costs, and improve overall network performance for Vodafone customers.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Vodafone is implementing agentic AI to transform its network operations, representing a major strategic shift toward autonomous network management. The initiative is described as a 'big bang' moment, signaling significant investment in AI-driven operational transformation.</t>
+          <t>Vodafone is deploying agentic AI to automate and self‑optimize its network operations. By leveraging machine learning and automation, the system dynamically manages traffic, optimizes performance, and reduces manual intervention. This initiative is positioned as a high‑impact transformation that will enhance reliability and operational efficiency.</t>
         </is>
       </c>
     </row>
@@ -2419,11 +2419,11 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2437,22 +2437,22 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>pilot</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>automation,machine learning,cloud AI,productivity tools</t>
+          <t>generative AI,LLM,automation,Microsoft Copilot,Azure OpenAI</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Enhanced internal productivity and operational efficiency through AI-powered automation.</t>
+          <t>Boost internal employee productivity, streamline workflows, and accelerate innovation across Vodafone's operations.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Vodafone is partnering with Microsoft to deploy AI-driven internal productivity solutions following a successful KPMG trial. This strategic initiative aims to transform Vodafone into an AI-powered technology communications powerhouse, with validated productivity gains driving the business case.</t>
+          <t>Vodafone is partnering with Microsoft to build an AI‑powered tech‑communications powerhouse, leveraging Microsoft’s Copilot and Azure OpenAI services to enhance internal productivity. A KPMG trial demonstrated tangible productivity gains, underscoring the initiative’s potential to transform employee workflows and drive operational efficiency.</t>
         </is>
       </c>
     </row>
@@ -2478,11 +2478,11 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2496,22 +2496,22 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>deployment</t>
+          <t>pilot</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>automation,machine learning,platform development</t>
+          <t>machine learning,automation</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Enables faster time-to-market for new mobile applications, improving operational efficiency and customer service delivery.</t>
+          <t>Accelerates development and launch of new mobile network applications, reducing time-to-market and improving customer experience.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Vodafone partners with Zinkworks to build an AI platform that accelerates the launch of mobile network apps. This initiative streamlines internal development processes to deliver new customer services more rapidly. The platform represents a strategic move to enhance digital agility and operational efficiency.</t>
+          <t>Vodafone partners with Zinkworks to build an AI-powered platform that streamlines and speeds up the creation of new mobile network applications. The platform uses machine learning and automation to reduce development effort and accelerate time-to-market for customer-facing apps. This initiative enhances Vodafone's ability to innovate quickly and deliver richer services to its users.</t>
         </is>
       </c>
     </row>
@@ -2541,11 +2541,11 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2564,17 +2564,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>machine learning,automation</t>
+          <t>machine learning,automation,model deployment,MLOps</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Accelerating service innovation and growth by empowering engineers to rapidly deploy AI models.</t>
+          <t>By empowering engineers to rapidly deploy AI models, Vodafone aims to accelerate service innovation and drive growth.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Vodafone is implementing an AI booster program that enables engineers to deploy new models, driving internal innovation. This initiative focuses on leveraging internal AI capabilities to fuel service growth and represents a strategic investment in operational transformation.</t>
+          <t>Vodafone is launching an internal AI booster program that equips engineers with tools to deploy new machine‑learning models quickly. This initiative enhances workforce productivity, enabling faster development of AI‑driven services that are expected to contribute to overall service growth.</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>network_optimization_performance</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>machine learning,automation,predictive analytics,NLP</t>
+          <t>machine learning,AI,automation,predictive analytics</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Enhanced competitive positioning through AI-driven improvements across multiple operational areas.</t>
+          <t>Improved network performance and reduced operational costs, enhancing customer experience and competitive positioning.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Vodafone is pursuing a comprehensive AI strategy spanning various use cases to achieve competitive advantage. The initiative addresses multiple business dimensions with noted benefits and implementation challenges. This reflects a strategic, large-scale commitment to AI transformation across the organization.</t>
+          <t>Vodafone is deploying AI‑driven network optimization to dynamically manage traffic, reduce latency, and improve QoS. By leveraging machine learning and automation, the operator can adapt to real‑time demand, boosting service quality and operational efficiency, giving it a competitive edge.</t>
         </is>
       </c>
     </row>
@@ -2665,11 +2665,11 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>internal_operations</t>
+          <t>internal_productivity_workforce</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2688,17 +2688,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>generative AI,automation,large language models</t>
+          <t>generative AI,LLM,automation,NLP</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Enhanced internal IT operational efficiency through AI-powered automation and expanded tool utilization.</t>
+          <t>Enables Vodafone employees to access and use IT tools more efficiently, reducing operational friction and accelerating decision-making across the organization.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Vodafone is collaborating with Capgemini to deploy Generative AI for expanding internal IT tool usage and automation capabilities. This initiative aims to boost internal productivity and streamline IT operations. It demonstrates Vodafone's strategic focus on leveraging AI for operational improvements.</t>
+          <t>Vodafone is partnering with Capgemini to deploy generative AI across its internal IT toolset, providing employees with AI‑powered assistants and automated workflows. This initiative enhances workforce productivity by streamlining routine tasks and improving knowledge retrieval, positioning Vodafone to operate more agilely and cost‑effectively.</t>
         </is>
       </c>
     </row>
@@ -2724,15 +2724,15 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>predictive_maintenance</t>
+          <t>predictive_maintenance_analytics</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>machine learning,automation,predictive analytics,anomaly detection</t>
+          <t>machine learning,predictive analytics,anomaly detection,root cause analysis,automation</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Proactive detection and automated resolution of network issues reduces downtime and improves service reliability.</t>
+          <t>Improved network reliability and reduced downtime by enabling faster detection and resolution of faults.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Vodafone is implementing AI to automatically detect and fix network issues, improving operational efficiency. This predictive maintenance initiative enhances network reliability and reduces manual intervention. The technology represents a strategic investment in core network infrastructure.</t>
+          <t>Vodafone is deploying AI-driven analytics to detect and automatically fix network issues. The system uses machine learning to identify anomalies and root causes, allowing rapid remediation. This enhances network uptime and reduces maintenance costs.</t>
         </is>
       </c>
     </row>
@@ -2772,8 +2772,14 @@
           <t>aimagazine.com | 500: Internal server error</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="C40" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Network Operations</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
@@ -2781,7 +2787,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2790,7 +2796,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2801,12 +2807,12 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Cannot determine - article returned 500 Internal Server Error and is inaccessible.</t>
+          <t>No AI initiative details available.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>The article about Vodafone's AI adoption on aimagazine.com is inaccessible due to a server error. No information can be extracted about their AI initiatives, use cases, or strategic direction.</t>
+          <t>The article is inaccessible, providing no information on AI applications within Vodafone's network operations. No specific AI use case can be identified.</t>
         </is>
       </c>
     </row>
@@ -2821,8 +2827,14 @@
           <t>sustainabilitymag.com | 500: Internal server error</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="C41" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Network-as-a-Sensor</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
@@ -2830,7 +2842,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2839,7 +2851,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2847,15 +2859,19 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>machine learning,sensor data,IoT</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Unable to determine due to inaccessible article (500 server error).</t>
+          <t>Potential to gather environmental data for sustainability initiatives, enabling Vodafone to monitor and reduce its ecological footprint.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>The article about Vodafone's AI initiative was inaccessible, returning a 500 Internal Server Error. No information could be extracted for analysis.</t>
+          <t>Vodafone is exploring the concept of using its network infrastructure as a sensor platform to collect environmental data for sustainability purposes. The initiative would leverage AI and IoT technologies to analyze sensor inputs, though specific implementation details and impact remain unclear.</t>
         </is>
       </c>
     </row>
@@ -2881,40 +2897,2205 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>customer_support</t>
+          <t>customer_support_experience</t>
         </is>
       </c>
       <c r="G42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>chatbot,NLP,automation,virtual assistant</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Improves customer support efficiency by reducing call wait times and enhancing issue resolution, leading to higher customer satisfaction and lower operational costs.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Vodafone is deploying AI-powered chatbots and virtual assistants to assist customers who call its call centre. The system uses natural language processing and automation to triage queries, provide instant answers, and route complex issues to human agents. This initiative aims to streamline support operations and improve the overall customer experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sky</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sky looks to AI to get smarter about customers - benefits, learnings and cautions</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>43221</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>pilot</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>AI,machine learning,natural language processing</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Improved customer understanding and service efficiency, enabling more personalized interactions and faster issue resolution.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Sky is exploring AI-driven solutions to better understand and serve its customers. The initiative focuses on using machine learning and natural language processing to analyze customer data and support interactions, aiming to deliver more tailored experiences. While the project promises benefits, the company acknowledges potential challenges and is currently in the pilot phase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sky</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sky flexes its AI muscles</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>43405</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sales / Customer Service</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>pilot</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>chatbot,NLP,automation</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Sky aims to enhance customer engagement and streamline sales interactions through AI-driven support, potentially boosting conversion rates and reducing support costs.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Sky is showcasing AI-powered customer support tools, such as chatbots and natural language processing, to assist customers and drive sales. The initiative focuses on automating routine inquiries and providing personalized recommendations, aiming to improve customer experience and operational efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sky</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sky turns to AI chatbots, cutting 2,000 call centre jobs - InfotechLead</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>45748</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
         <v>0.95</v>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>deployment</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>voice AI,NLP,automation,speech recognition,virtual assistant</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Enhanced customer service efficiency and reduced call handling times while improving customer satisfaction.</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Vodafone is implementing AI-powered assistance for customers calling its contact centers, marking a significant advancement in phone-based customer support. This initiative leverages voice AI and natural language processing to improve service quality and operational efficiency. The deployment represents Vodafone's strategic push toward AI-driven customer experience transformation.</t>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>chatbot,NLP,automation</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Sky is cutting 2,000 call centre jobs by deploying AI chatbots, reducing operational costs and streamlining customer support processes.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Sky is deploying AI-powered chatbots to handle customer queries, leveraging natural language processing and automation to replace traditional call centre staff. This initiative aims to cut 2,000 jobs and lower support costs while maintaining service availability, marking a significant shift in its customer service strategy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sky</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Post | LinkedIn</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Hosted internal AI Competition</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>internal_productivity_workforce</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>pilot</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>AI,machine learning,generative AI</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Fosters employee innovation and accelerates the development of AI-driven solutions that can enhance operational efficiency and support future product initiatives.</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Sky hosted an internal AI competition to encourage employees to develop AI and machine learning solutions for internal challenges. The initiative aims to unlock new ideas, improve workforce productivity, and identify potential AI applications across the organization. By engaging staff in hands‑on AI development, Sky seeks to accelerate innovation and create a culture of continuous improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TalkTalk</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Broadband ISP TalkTalk UK Adopt NiCE's AI-Powered Customer Service Platform - ISPreview UK</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>chatbot,NLP,automation,LLM</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>TalkTalk expects faster response times, higher first‑contact resolution rates, and reduced support costs through automated, AI‑driven customer interactions.</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>TalkTalk UK has adopted NiCE’s AI‑powered customer service platform, deploying chatbots and virtual assistants that use natural language processing to answer customer queries and troubleshoot issues. This initiative enhances the customer experience and streamlines support operations, positioning TalkTalk to compete more effectively in the broadband market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TalkTalk</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TalkTalk partners with Kraken to revolutionise customer experience for millions of UK broadband customers - TalkTalk Group</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>45748</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>chatbot,NLP,automation,LLM</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Enhanced customer support efficiency and satisfaction, reducing response times and operational costs while scaling service to millions of broadband users.</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>TalkTalk has partnered with Kraken to deploy AI‑powered chatbots and virtual assistants that use natural language processing to handle customer queries and troubleshooting. This initiative transforms the broadband customer experience by providing instant, automated support at scale, improving satisfaction and reducing support costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TalkTalk</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MD Tech Leader Talks with Phil Haslam, CTO at TalkTalk - The roundup | Manchester Digital</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Unsure</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Internal Productivity / Network Ops</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>internal_productivity_workforce</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>automation,machine learning</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Enhanced employee efficiency and streamlined network operations through AI-driven tools.</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>TalkTalk's CTO discusses how the company is leveraging AI to boost internal productivity and support network operations. By automating routine tasks and providing intelligent insights, the initiative aims to improve staff efficiency and network reliability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TalkTalk</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Personalising the journey to full fibre | CityFibre</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>45017</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>machine learning,recommendation engine</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>By personalising the fibre adoption journey, TalkTalk improves customer satisfaction and accelerates full‑fibre uptake, translating into higher conversion rates and stronger competitive positioning.</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>TalkTalk leverages AI‑driven recommendation engines to tailor the full‑fibre rollout experience for each customer. The system analyses customer data to suggest optimal plans and pathways, enhancing engagement and speeding adoption. This customer‑centric AI initiative boosts satisfaction and drives higher fibre penetration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Glide</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>No Mentions Identified</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>No mentions in public domain</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>No AI initiatives were identified; impact cannot be determined.</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No AI applications were identified in Glide's public domain materials. Therefore, no specific use case, technology, or business impact can be described.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Introducing Beni: Advanced AI Integration for Zen Internet Customer Support | CBM Digital</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>45413</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>chatbot,NLP,LLM,generative AI</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Zen Internet expects faster response times and higher customer satisfaction by automating routine support queries with Beni, its new AI-powered assistant.</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Zen Internet launches Beni, an AI-driven customer support solution that leverages advanced natural language processing and large language models to handle common queries automatically. By integrating Beni into its support channels, Zen aims to reduce response times, free up human agents for complex issues, and enhance overall customer experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Utility Warehouse</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Utility Warehouse Case Study  |  Google Cloud Documentation</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Unsure</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AI / ML</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>chatbot,NLP,machine learning</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Enhanced customer service efficiency and satisfaction through AI-powered chatbots, reducing response times and freeing staff for complex queries.</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Utility Warehouse uses Google Cloud AI and NLP to deploy chatbots that handle routine customer inquiries, improving response times and overall customer experience. This initiative represents a strategic effort to modernize support operations and elevate service quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Utility Warehouse</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Utility Warehouse streamlines success</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Unsure</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>chatbot,NLP,automation</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Enhanced customer support efficiency and satisfaction by automating routine inquiries and streamlining issue resolution.</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Utility Warehouse is deploying AI-powered chatbots and natural language processing tools to improve its customer service operations. By automating routine queries and providing instant support, the company aims to reduce response times and increase customer satisfaction, contributing to overall operational success.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Cuckoo</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>No Mentions Identified</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>No mentions in public domain</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>No AI initiatives identified; impact unknown.</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No AI initiatives identified for Cuckoo; no public information is available regarding AI applications or deployments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>YouFibre / Brsk</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Post | LinkedIn</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Internal Productivity</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>internal_productivity_workforce</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>pilot</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>generative AI,LLM,automation</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Boosts employee productivity by automating routine tasks and improving knowledge retrieval.</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>YouFibre/Brsk is introducing an AI-powered internal productivity tool that leverages generative AI and large language models to streamline employee workflows and knowledge management. The solution automates routine tasks and provides quick access to information, enhancing overall operational efficiency. This initiative underscores the company's commitment to modernizing its workforce tools.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>YouFibre / Brsk</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Brsk launches WhatsApp chat support | thinkbroadband</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>45444</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>chatbot,NLP,automation,WhatsApp API</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>The AI‑powered WhatsApp chatbot is expected to reduce response times, increase self‑service resolution rates, and boost overall customer satisfaction for Brsk.</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Brsk has launched an AI‑driven chatbot on WhatsApp to provide instant customer support. Leveraging natural language processing and automation, the bot handles common queries and escalates complex issues, enhancing the customer experience and freeing up human agents for higher‑value tasks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Openreach</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Openreach AI Chatbots and Data Analytics Aid Network Management - ISPreview UK</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>43497</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>chatbot,NLP,machine learning,data analytics</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Enhances customer support by automating query handling and improves network management through real‑time analytics, leading to faster issue resolution and more efficient network operations.</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Openreach is deploying AI-powered chatbots that use natural language processing to handle customer queries, while simultaneously leveraging data analytics to support network management. This dual approach improves customer experience and operational efficiency, positioning Openreach to respond more quickly to service issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Openreach</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Openreach turns to video AI to cut install snags | Operations | TelcoTitans.com</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>44562</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Network Operations</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>internal_productivity_workforce</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>computer vision,video AI,machine learning,automation</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>By using video AI to identify and eliminate installation snags, Openreach can reduce errors, shorten deployment times, and lower labor costs.</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Openreach is deploying video AI, a computer vision solution, to monitor installers and detect common snags in real time. This tool improves operational efficiency by reducing mistakes during fiber installation, leading to faster rollouts and cost savings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Openreach</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Post | LinkedIn</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Internal Productivity</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>internal_productivity_workforce</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>automation,machine learning,LLM</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Boosts employee productivity by automating routine tasks and providing AI-driven assistance, leading to faster project turnaround and reduced operational overhead.</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Openreach is deploying AI-powered internal productivity tools, such as automated workflow assistants and large language model-based knowledge bases, to streamline employee tasks. These solutions help staff quickly retrieve information, draft documents, and manage routine processes, ultimately improving efficiency and freeing up time for higher-value work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Openreach</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Openreach-Annual-Review-2023 online.pdf</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>45261</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>chatbot,NLP,automation</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Enhanced customer support efficiency and satisfaction through AI-driven self-service and automated ticket handling.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Openreach is leveraging AI-powered chatbots and natural language processing to streamline customer service interactions. By automating routine queries and providing instant assistance, the company aims to improve response times and reduce operational costs. This initiative underscores Openreach’s commitment to delivering a more efficient and customer‑centric experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CityFibre</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Personalising the journey to full fibre | CityFibre</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>45017</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>machine learning,recommendation engine,natural language processing,automation</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Enhanced customer experience and accelerated fibre adoption by tailoring the deployment journey to individual needs, leading to higher conversion rates and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>CityFibre is leveraging AI-driven personalization to tailor the customer journey toward full fibre connectivity. By using machine learning recommendation engines and NLP-based interactions, the company customizes offers, timelines, and support for each prospect. This approach improves conversion rates and customer satisfaction, driving faster market penetration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CityFibre</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CityFibre and IQGeo customer story | IQGeo</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Unsure</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Network Operations</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>network_planning_deployment</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>machine learning,AI,predictive analytics,optimization algorithms</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>CityFibre is using IQGeo’s AI‑driven planning tools to accelerate fibre rollout, reduce CAPEX, and improve network performance, driving faster service delivery and cost savings.</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>CityFibre has partnered with IQGeo to deploy AI‑powered network planning and design solutions. The technology uses machine learning and predictive analytics to optimise fibre routes, capacity and deployment schedules, enabling faster, cheaper and more reliable network rollouts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CityFibre</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Cityfibre prioritizes automation for “friction free” customer journeys</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>45139</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Customer Service / Internal Productivity</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>automation,machine learning,NLP,chatbot</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Streamlines customer interactions, reducing friction and improving satisfaction.</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>CityFibre is deploying AI‑driven automation to create friction‑free customer journeys. The initiative uses chatbots and NLP to handle routine queries and guide customers through service processes, aiming to enhance the overall customer experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CityFibre</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Using AI to power a new era of customer service quality | CityFibre</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>44835</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>chatbot,NLP,automation,virtual assistant</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>CityFibre expects faster response times, higher customer satisfaction, and reduced support costs through AI‑powered customer service.</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>CityFibre is deploying AI‑driven chatbots and virtual assistants that use natural language processing to handle customer queries and troubleshoot issues. This initiative aims to elevate service quality, streamline support operations, and provide a competitive edge in the broadband market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CityFibre</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Post | LinkedIn</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>45597</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Created a snowflake data cloud to enable AI</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Snowflake,data cloud,AI,machine learning</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Enables CityFibre to deploy AI solutions across the organization by providing a scalable, cloud-based data platform.</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>CityFibre has launched a Snowflake-based data cloud to support its AI initiatives. The platform offers a unified, scalable data foundation that can be leveraged for future AI and machine learning projects, positioning the company to accelerate innovation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Netomnia</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Netomnia</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Created internal platform which unifies all data - Odin</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>machine learning,NLP,automation,data integration</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>The Odin platform enables AI-driven customer support, reducing response times and improving resolution rates for Netomnia’s customers.</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Netomnia has launched Odin, an internal platform that consolidates all customer data to feed AI models. By integrating machine learning and NLP, the platform powers automated support tools that streamline ticket handling and enhance the customer experience. This initiative positions Netomnia to deliver faster, more accurate service at scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>nexfibre</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>No Mentions Identified</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>No mentions in public domain - should caveat that they are owned by VMO2 so in practice would have initatives</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>No publicly disclosed AI initiatives, so impact cannot be determined.</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No AI initiatives were identified for nexfibre in the public domain. As a subsidiary of VMO2, any potential AI projects are not publicly disclosed, leaving the company's AI strategy unclear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Hyperoptic</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Post | LinkedIn</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Customer Service / Hyperpersonalisation</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>chatbot,NLP,machine learning,LLM</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Enhanced customer experience through AI-driven personalized support, leading to higher satisfaction and reduced support ticket volume.</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Hyperoptic is deploying AI-powered chatbots and personalization engines to deliver hyperpersonalised customer support. By leveraging NLP and machine learning, the company can tailor responses and recommendations to individual users in real time. This initiative aims to improve customer satisfaction and reduce support workload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Community Fibre</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Community Fibre partners with Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>45170</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Customer Service / Hyperpersonalisation</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>customer_support_experience</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>pilot</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>chatbot,NLP,machine learning,automation</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Enhances customer support with AI-driven personalization, improving response times and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Community Fibre has partnered with AWS to deploy AI‑powered customer service solutions, including chatbots and natural language processing for hyperpersonalised support. The collaboration aims to automate routine queries and tailor interactions, boosting response efficiency and customer satisfaction. This partnership positions Community Fibre to elevate its customer experience through advanced AI capabilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Community Fibre</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CommunityFibre Adopt AI-Driven Analytics to Improve Home WiFi - ISPreview UK</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>44409</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>network_optimization_performance</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>machine learning,predictive analytics</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Enhanced home WiFi performance leading to improved customer satisfaction and reduced support tickets.</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Community Fibre is leveraging AI-driven analytics to optimize home WiFi performance. By analyzing network data, the system identifies and addresses performance bottlenecks, improving connectivity for customers. This initiative enhances customer experience and reduces support workload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Community Fibre</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>How Community Fibre 12x’d Their Customer Base While Keeping Customer Support Contacts Flat with Yext | Yext</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Unsure</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AI SEO</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>AI,machine learning,NLP,automation</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Community Fibre grew its customer base 12x while keeping customer support contacts flat, demonstrating efficient acquisition and support scaling.</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Community Fibre leveraged Yext’s AI‑powered SEO tools to dramatically expand its customer base. By automating search engine optimization and content management, the company attracted more customers without increasing support call volume, underscoring the strategic value of AI in marketing and customer acquisition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FullFibre</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FullFibre partners with Gigabit IQ</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Network Operations</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>network_optimization_performance</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>machine learning,AI,network optimization,predictive analytics</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Enhanced network performance and reliability through AI‑driven optimization, leading to lower latency and higher customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>FullFibre has teamed up with Gigabit IQ to deploy AI‑driven network optimization solutions. The partnership leverages machine‑learning models to monitor and adjust traffic in real time, improving bandwidth allocation and reducing latency. This move is expected to boost network reliability and customer experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Gigaclear</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Rural UK ISP Gigaclear Adopts AI to Improve Customer Broadband Installs - ISPreview UK</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Network Operations</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>network_planning_deployment</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>machine learning,automation,predictive analytics</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Improves installation efficiency and reduces deployment time and cost, leading to higher customer satisfaction and faster network roll‑out.</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Gigaclear is deploying AI‑driven tools to optimise broadband installation processes, using machine learning to predict optimal routes, resource needs and scheduling. By automating these planning tasks, the ISP can accelerate roll‑outs and cut installation costs, enhancing service delivery in rural areas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Gigaclear</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Gigaclear adopts the Aiimi Insight Engine - Aiimi</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>44986</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>security_fraud_threat</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>machine learning,predictive analytics,automation</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Gigaclear can monitor regulatory compliance in real time, reducing the risk of fines and improving audit readiness.</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Gigaclear has adopted the Aiimi Insight Engine, an AI-powered compliance platform that analyzes network and operational data to detect regulatory breaches. By automating compliance monitoring, the company enhances risk management and ensures adherence to industry standards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Gigaclear</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Gigaclear | WorkRamp</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Unsure</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Internal Productivity</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>internal_productivity_workforce</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>AI,automation,learning management system</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Accelerates employee onboarding and training, reducing ramp‑up time and increasing workforce productivity.</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Gigaclear is implementing WorkRamp, an AI‑enhanced learning platform, to streamline internal onboarding and training processes. By automating content delivery and personalizing learning paths, the company improves employee productivity and reduces time to competency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Gigaclear</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Gigaclear enhances telephony services with Oculeus' RVM</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>45231</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Fraud Detection</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>security_fraud_threat</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>machine learning,voice biometrics,speech recognition</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Reduces fraudulent calls and revenue loss, improving security and customer trust.</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Gigaclear has partnered with Oculeus to deploy the RVM solution, an AI-powered fraud detection system that monitors voice traffic in real time. By identifying and blocking fraudulent calls, the system enhances the security of its telephony services and protects revenue streams. This integration demonstrates Gigaclear’s commitment to safeguarding customers and maintaining service integrity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>APFN</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>No Mentions Identified</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>No mentions in public domain</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>No AI initiatives identified.</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No AI usage reported for APFN in the public domain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ITS</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>No Mentions Identified</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>No mentions in public domain</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No AI-related information was found for ITS in the public domain.</t>
         </is>
       </c>
     </row>
